--- a/data/trans_orig/P27_1-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P27_1-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los días de diario en 2007</t>
+          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los días de diario en 2007 (tasa de respuesta: 94,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7800</t>
+          <t>8326</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25424</t>
+          <t>24893</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8014</t>
+          <t>7822</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23481</t>
+          <t>23418</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20117</t>
+          <t>18894</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44045</t>
+          <t>41552</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71179</t>
+          <t>73532</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>105341</t>
+          <t>106789</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30341</t>
+          <t>30054</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54931</t>
+          <t>54162</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>110347</t>
+          <t>108303</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>151116</t>
+          <t>153222</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>188853</t>
+          <t>188985</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>232010</t>
+          <t>232474</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>150295</t>
+          <t>152622</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>185023</t>
+          <t>185203</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>351979</t>
+          <t>345498</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>403722</t>
+          <t>404424</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,51%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>116258</t>
+          <t>117027</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>155983</t>
+          <t>156841</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56419</t>
+          <t>54414</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>84338</t>
+          <t>82849</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>182568</t>
+          <t>179986</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>231210</t>
+          <t>232024</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,27%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11949</t>
+          <t>11200</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31917</t>
+          <t>30662</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10353</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27422</t>
+          <t>26601</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>26031</t>
+          <t>27607</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>50326</t>
+          <t>51920</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53270</t>
+          <t>52412</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>83082</t>
+          <t>83418</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46873</t>
+          <t>49192</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74462</t>
+          <t>77327</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>108804</t>
+          <t>108309</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>150091</t>
+          <t>149485</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,2%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>132957</t>
+          <t>133887</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>172244</t>
+          <t>172346</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>152579</t>
+          <t>149457</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>190074</t>
+          <t>189341</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>293992</t>
+          <t>294875</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>347689</t>
+          <t>349771</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,6%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>98925</t>
+          <t>99792</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>135987</t>
+          <t>137197</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>83483</t>
+          <t>84128</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>118344</t>
+          <t>119674</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>193739</t>
+          <t>192832</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>242782</t>
+          <t>244902</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,73%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>47610</t>
+          <t>49051</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>79877</t>
+          <t>78501</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6186</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19830</t>
+          <t>19290</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>57158</t>
+          <t>58092</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>90393</t>
+          <t>90834</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,22%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>83245</t>
+          <t>81198</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>119003</t>
+          <t>118728</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19545</t>
+          <t>19167</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38556</t>
+          <t>38500</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>107822</t>
+          <t>107389</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>148412</t>
+          <t>149183</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>187175</t>
+          <t>191131</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>236311</t>
+          <t>235437</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52625</t>
+          <t>53913</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76959</t>
+          <t>78176</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>253389</t>
+          <t>255375</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>304316</t>
+          <t>308326</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,88%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>128767</t>
+          <t>131736</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>171010</t>
+          <t>172560</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45269</t>
+          <t>44017</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>70071</t>
+          <t>67770</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>182639</t>
+          <t>182983</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>230610</t>
+          <t>230948</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,62%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>98905</t>
+          <t>100598</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>142534</t>
+          <t>142085</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34406</t>
+          <t>34131</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>60172</t>
+          <t>60091</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>139988</t>
+          <t>142206</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>191104</t>
+          <t>191590</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>231068</t>
+          <t>233044</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>289223</t>
+          <t>292445</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>99133</t>
+          <t>101442</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>138685</t>
+          <t>141427</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>347906</t>
+          <t>344197</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>412950</t>
+          <t>414398</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>386092</t>
+          <t>387333</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>455942</t>
+          <t>451877</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>280649</t>
+          <t>279802</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>334380</t>
+          <t>329469</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>685811</t>
+          <t>686140</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>770225</t>
+          <t>771229</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,64%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>340563</t>
+          <t>339923</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>403144</t>
+          <t>404700</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>189798</t>
+          <t>188753</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>236077</t>
+          <t>237992</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>543912</t>
+          <t>545258</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>621270</t>
+          <t>625739</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,79%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24473</t>
+          <t>24649</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>46672</t>
+          <t>46542</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>31088</t>
+          <t>31163</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>56686</t>
+          <t>57442</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>60741</t>
+          <t>62977</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>95482</t>
+          <t>94165</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>68085</t>
+          <t>67478</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>99875</t>
+          <t>100445</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>62846</t>
+          <t>63988</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>97388</t>
+          <t>97034</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>141589</t>
+          <t>140889</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>185979</t>
+          <t>184947</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,57%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>83059</t>
+          <t>83798</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>117000</t>
+          <t>118138</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>173112</t>
+          <t>173361</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>219340</t>
+          <t>218768</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>269298</t>
+          <t>267297</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>325148</t>
+          <t>324448</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,85%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>90334</t>
+          <t>90469</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>123636</t>
+          <t>123861</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>193645</t>
+          <t>192204</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>239774</t>
+          <t>239070</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>295491</t>
+          <t>295439</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>352038</t>
+          <t>353561</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>41,24%</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15174</t>
+          <t>16053</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14709</t>
+          <t>14965</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32322</t>
+          <t>33689</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>20995</t>
+          <t>22624</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>43206</t>
+          <t>44441</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>42379</t>
+          <t>42508</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>67979</t>
+          <t>68479</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>118411</t>
+          <t>120173</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>163321</t>
+          <t>163211</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>170816</t>
+          <t>171759</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>221540</t>
+          <t>223107</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>100893</t>
+          <t>99740</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>132044</t>
+          <t>132732</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>377834</t>
+          <t>375870</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>442711</t>
+          <t>441613</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>491177</t>
+          <t>491285</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>567531</t>
+          <t>562012</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,14%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>87693</t>
+          <t>86710</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>118076</t>
+          <t>117055</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>582506</t>
+          <t>584335</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>650899</t>
+          <t>655133</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>682582</t>
+          <t>682060</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>760729</t>
+          <t>763143</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,79%</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>229025</t>
+          <t>231715</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>292478</t>
+          <t>292793</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4162,12 +4162,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>131993</t>
+          <t>132760</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>181924</t>
+          <t>179741</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>375302</t>
+          <t>379557</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>454463</t>
+          <t>458912</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -4260,12 +4260,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>606680</t>
+          <t>602816</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>695908</t>
+          <t>695718</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4295,12 +4295,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>426083</t>
+          <t>430228</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>506732</t>
+          <t>513334</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1061874</t>
+          <t>1061181</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1187843</t>
+          <t>1182722</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4345,12 +4345,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,72%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1151291</t>
+          <t>1157228</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1262723</t>
+          <t>1268469</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1263302</t>
+          <t>1267219</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1378776</t>
+          <t>1374281</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2450188</t>
+          <t>2445979</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2609152</t>
+          <t>2601144</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,18%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>935867</t>
+          <t>940267</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1037990</t>
+          <t>1040785</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1215043</t>
+          <t>1213787</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1325253</t>
+          <t>1324300</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2181405</t>
+          <t>2178799</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2325465</t>
+          <t>2335714</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,98%</t>
         </is>
       </c>
     </row>
@@ -4755,7 +4755,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los días de diario en 2012</t>
+          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los días de diario en 2012 (tasa de respuesta: 96,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6782</t>
+          <t>7796</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7426</t>
+          <t>7375</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1126</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10852</t>
+          <t>10860</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>6055</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19996</t>
+          <t>21960</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5078,12 +5078,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7256</t>
+          <t>7511</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22570</t>
+          <t>22718</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5113,12 +5113,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16728</t>
+          <t>17107</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38397</t>
+          <t>37131</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5148,12 +5148,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -5176,12 +5176,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57005</t>
+          <t>57050</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>87306</t>
+          <t>89023</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5191,12 +5191,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16300</t>
+          <t>16297</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37779</t>
+          <t>36366</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>78705</t>
+          <t>76985</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116733</t>
+          <t>116573</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5261,12 +5261,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -5289,12 +5289,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>319151</t>
+          <t>318682</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>352359</t>
+          <t>352666</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>243028</t>
+          <t>243291</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>268369</t>
+          <t>268959</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5339,12 +5339,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>572848</t>
+          <t>571392</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>615439</t>
+          <t>614973</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5374,12 +5374,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,42%</t>
         </is>
       </c>
     </row>
@@ -5519,12 +5519,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16249</t>
+          <t>15674</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3076</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15125</t>
+          <t>13238</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5569,12 +5569,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>9012</t>
+          <t>9331</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>24856</t>
+          <t>23967</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5604,12 +5604,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -5632,12 +5632,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5646</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20590</t>
+          <t>21210</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5647,12 +5647,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>4918</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20120</t>
+          <t>19606</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13456</t>
+          <t>13209</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33046</t>
+          <t>33018</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44437</t>
+          <t>43962</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74960</t>
+          <t>75528</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39119</t>
+          <t>39331</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69566</t>
+          <t>68505</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>91342</t>
+          <t>89459</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>133731</t>
+          <t>132502</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5830,12 +5830,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -5858,12 +5858,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>301891</t>
+          <t>300716</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>336515</t>
+          <t>336789</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>236938</t>
+          <t>237987</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>269824</t>
+          <t>270073</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>550550</t>
+          <t>551904</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>597463</t>
+          <t>597059</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5943,12 +5943,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,64%</t>
         </is>
       </c>
     </row>
@@ -6088,12 +6088,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7932</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21796</t>
+          <t>22078</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6650</t>
+          <t>6551</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9013</t>
+          <t>8994</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24003</t>
+          <t>24671</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -6201,12 +6201,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24584</t>
+          <t>24155</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47862</t>
+          <t>47782</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2967</t>
+          <t>3041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14373</t>
+          <t>14218</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>30863</t>
+          <t>30789</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>54304</t>
+          <t>56109</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -6314,12 +6314,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57422</t>
+          <t>58561</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>90328</t>
+          <t>92028</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6329,12 +6329,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15096</t>
+          <t>14008</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33747</t>
+          <t>32366</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77369</t>
+          <t>78202</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>115029</t>
+          <t>115315</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -6427,12 +6427,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>473856</t>
+          <t>474073</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>513314</t>
+          <t>514259</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>207771</t>
+          <t>207399</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>228117</t>
+          <t>228104</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>689684</t>
+          <t>689670</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>734810</t>
+          <t>735558</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,84%</t>
         </is>
       </c>
     </row>
@@ -6657,12 +6657,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21487</t>
+          <t>21431</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43283</t>
+          <t>42648</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6186</t>
+          <t>6951</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20649</t>
+          <t>22375</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30649</t>
+          <t>31600</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57737</t>
+          <t>58531</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -6770,12 +6770,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34231</t>
+          <t>35432</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>62783</t>
+          <t>63251</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6785,12 +6785,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29441</t>
+          <t>29995</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>54969</t>
+          <t>55943</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>71484</t>
+          <t>71664</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>109792</t>
+          <t>109738</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>111300</t>
+          <t>110702</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>154006</t>
+          <t>156155</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>70859</t>
+          <t>70331</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>108067</t>
+          <t>105583</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>190939</t>
+          <t>192164</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>246520</t>
+          <t>248117</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -6996,12 +6996,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>888199</t>
+          <t>891220</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>944762</t>
+          <t>946001</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7011,12 +7011,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>576888</t>
+          <t>580316</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>620010</t>
+          <t>622981</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1482541</t>
+          <t>1485033</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1553033</t>
+          <t>1550347</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>82,92%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>4540</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16957</t>
+          <t>16541</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12562</t>
+          <t>14012</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>31552</t>
+          <t>32696</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21090</t>
+          <t>19901</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>43077</t>
+          <t>42439</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -7339,12 +7339,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21637</t>
+          <t>21161</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>43873</t>
+          <t>43766</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15876</t>
+          <t>15115</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36102</t>
+          <t>36406</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>42065</t>
+          <t>41909</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>71627</t>
+          <t>72178</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -7452,12 +7452,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>43829</t>
+          <t>43640</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>72234</t>
+          <t>72321</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7467,12 +7467,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>54547</t>
+          <t>53454</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>87799</t>
+          <t>87642</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>105044</t>
+          <t>105325</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>152152</t>
+          <t>147007</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -7565,12 +7565,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>381676</t>
+          <t>378568</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>416929</t>
+          <t>415790</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>608622</t>
+          <t>607749</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>649244</t>
+          <t>650580</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1002690</t>
+          <t>1003462</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1058767</t>
+          <t>1055128</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>84,92%</t>
         </is>
       </c>
     </row>
@@ -7800,7 +7800,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6841</t>
+          <t>8019</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4925</t>
+          <t>5163</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>18749</t>
+          <t>18711</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6896</t>
+          <t>6764</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>21817</t>
+          <t>22099</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6615</t>
+          <t>6807</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>20297</t>
+          <t>20858</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>28762</t>
+          <t>28410</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>52960</t>
+          <t>53668</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>39383</t>
+          <t>38829</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>67097</t>
+          <t>66721</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -8021,12 +8021,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>38901</t>
+          <t>38032</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>63820</t>
+          <t>62612</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8036,12 +8036,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>94275</t>
+          <t>93383</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>135708</t>
+          <t>134585</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>141218</t>
+          <t>140174</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>188491</t>
+          <t>186863</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -8134,12 +8134,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>182480</t>
+          <t>183616</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>210110</t>
+          <t>210528</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>875454</t>
+          <t>877645</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>923114</t>
+          <t>923947</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8184,12 +8184,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1068361</t>
+          <t>1071052</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1124238</t>
+          <t>1125479</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8219,12 +8219,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,86%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>51806</t>
+          <t>52282</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>83810</t>
+          <t>83685</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>42029</t>
+          <t>41939</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>71617</t>
+          <t>72130</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8419,7 +8419,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>101590</t>
+          <t>99062</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>146550</t>
+          <t>143457</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>125524</t>
+          <t>125373</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>173345</t>
+          <t>174840</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>114474</t>
+          <t>111843</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>164187</t>
+          <t>160164</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>253209</t>
+          <t>251715</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>320067</t>
+          <t>317485</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>400908</t>
+          <t>398759</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>482069</t>
+          <t>477643</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>330046</t>
+          <t>332447</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>408834</t>
+          <t>408947</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8640,12 +8640,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>755438</t>
+          <t>754373</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>863107</t>
+          <t>863474</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -8703,12 +8703,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2620022</t>
+          <t>2620305</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2716250</t>
+          <t>2716838</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2812240</t>
+          <t>2817059</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2907444</t>
+          <t>2907040</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>5472931</t>
+          <t>5470580</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5598614</t>
+          <t>5597464</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,95%</t>
         </is>
       </c>
     </row>
@@ -8972,7 +8972,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los días de diario en 2016</t>
+          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los días de diario en 2016 (tasa de respuesta: 97,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9167,12 +9167,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12143</t>
+          <t>10921</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2757</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>13838</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9217,12 +9217,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5565</t>
+          <t>5700</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19191</t>
+          <t>19409</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9252,12 +9252,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -9280,12 +9280,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9053</t>
+          <t>8896</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26367</t>
+          <t>27442</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9295,12 +9295,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10581</t>
+          <t>10112</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26060</t>
+          <t>26792</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9330,12 +9330,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21803</t>
+          <t>22092</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44968</t>
+          <t>46611</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9365,12 +9365,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -9393,12 +9393,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>54206</t>
+          <t>55924</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>86453</t>
+          <t>89537</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9408,12 +9408,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37030</t>
+          <t>37573</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>63010</t>
+          <t>62025</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>100167</t>
+          <t>102538</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>140792</t>
+          <t>143140</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>
@@ -9506,12 +9506,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>312386</t>
+          <t>313293</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>348825</t>
+          <t>348233</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>250898</t>
+          <t>252671</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>281235</t>
+          <t>281475</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>575616</t>
+          <t>574536</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>620535</t>
+          <t>620962</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,52%</t>
         </is>
       </c>
     </row>
@@ -9736,12 +9736,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10557</t>
+          <t>10113</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9751,12 +9751,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9771,12 +9771,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14952</t>
+          <t>15494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9806,12 +9806,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>5832</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>20563</t>
+          <t>20543</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11905</t>
+          <t>12027</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30252</t>
+          <t>30041</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17743</t>
+          <t>16684</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38290</t>
+          <t>37622</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34443</t>
+          <t>33395</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63305</t>
+          <t>59886</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9934,12 +9934,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -9962,12 +9962,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51757</t>
+          <t>52465</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>81971</t>
+          <t>81024</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40017</t>
+          <t>41660</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68181</t>
+          <t>68306</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>101408</t>
+          <t>101421</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141709</t>
+          <t>142271</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10052,7 +10052,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -10075,12 +10075,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>259110</t>
+          <t>259945</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>294417</t>
+          <t>293924</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10090,12 +10090,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>258233</t>
+          <t>258948</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>290442</t>
+          <t>292294</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>527619</t>
+          <t>530078</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>576557</t>
+          <t>575881</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,76%</t>
         </is>
       </c>
     </row>
@@ -10305,12 +10305,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13318</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32646</t>
+          <t>31953</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10274</t>
+          <t>10080</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15584</t>
+          <t>16419</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36695</t>
+          <t>37803</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -10418,12 +10418,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22719</t>
+          <t>23294</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46654</t>
+          <t>46244</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10433,12 +10433,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12847</t>
+          <t>13317</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10468,12 +10468,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>28409</t>
+          <t>28663</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>53048</t>
+          <t>50872</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -10531,12 +10531,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>78163</t>
+          <t>77008</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>114374</t>
+          <t>114800</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18664</t>
+          <t>17843</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37622</t>
+          <t>37419</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>100875</t>
+          <t>101965</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>142266</t>
+          <t>142346</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,33%</t>
         </is>
       </c>
     </row>
@@ -10644,12 +10644,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>340031</t>
+          <t>336884</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>380183</t>
+          <t>381063</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10659,12 +10659,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>110214</t>
+          <t>110050</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>131194</t>
+          <t>131780</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10694,12 +10694,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>456774</t>
+          <t>458536</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>505524</t>
+          <t>503646</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10729,12 +10729,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,47%</t>
         </is>
       </c>
     </row>
@@ -10874,12 +10874,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23213</t>
+          <t>23345</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47661</t>
+          <t>48291</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20032</t>
+          <t>20836</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40958</t>
+          <t>42214</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>48489</t>
+          <t>48150</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81000</t>
+          <t>79838</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10959,12 +10959,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -10987,12 +10987,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>76366</t>
+          <t>79411</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>115959</t>
+          <t>116172</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45888</t>
+          <t>45964</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>75497</t>
+          <t>76441</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>133087</t>
+          <t>131388</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>180268</t>
+          <t>183263</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11072,12 +11072,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -11100,12 +11100,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>195798</t>
+          <t>195265</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>252244</t>
+          <t>249955</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11135,12 +11135,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>151696</t>
+          <t>151686</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>198458</t>
+          <t>197872</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>362133</t>
+          <t>361867</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>431798</t>
+          <t>434005</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11185,12 +11185,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,5%</t>
         </is>
       </c>
     </row>
@@ -11213,12 +11213,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>736549</t>
+          <t>737162</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>801304</t>
+          <t>798795</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>518091</t>
+          <t>515737</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>570286</t>
+          <t>569832</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11263,12 +11263,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1265738</t>
+          <t>1268331</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1348638</t>
+          <t>1351608</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11298,12 +11298,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>70,08%</t>
         </is>
       </c>
     </row>
@@ -11443,12 +11443,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9424</t>
+          <t>9687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26140</t>
+          <t>26206</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11478,12 +11478,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6828</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20036</t>
+          <t>20518</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>18721</t>
+          <t>19408</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>40334</t>
+          <t>40157</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11528,12 +11528,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -11556,12 +11556,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22792</t>
+          <t>22032</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44283</t>
+          <t>44308</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11591,12 +11591,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24657</t>
+          <t>24284</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>47937</t>
+          <t>49323</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11626,12 +11626,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>51136</t>
+          <t>53627</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>85477</t>
+          <t>85922</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11641,12 +11641,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -11669,12 +11669,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>81689</t>
+          <t>84719</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>121378</t>
+          <t>122762</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11704,12 +11704,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>82941</t>
+          <t>83124</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>121350</t>
+          <t>119999</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11739,12 +11739,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>177828</t>
+          <t>173273</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>229034</t>
+          <t>228778</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11754,12 +11754,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -11782,12 +11782,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>440703</t>
+          <t>439309</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>484778</t>
+          <t>483503</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11797,12 +11797,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11817,12 +11817,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>548050</t>
+          <t>548398</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>592374</t>
+          <t>593489</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11832,12 +11832,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11852,12 +11852,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1002412</t>
+          <t>1003724</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1066573</t>
+          <t>1067897</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11867,12 +11867,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,13%</t>
         </is>
       </c>
     </row>
@@ -12012,12 +12012,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11712</t>
+          <t>11507</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12027,12 +12027,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14384</t>
+          <t>13854</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32545</t>
+          <t>34222</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12062,12 +12062,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12082,12 +12082,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>18696</t>
+          <t>19303</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>40674</t>
+          <t>42074</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12097,12 +12097,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -12125,12 +12125,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17303</t>
+          <t>17292</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>37681</t>
+          <t>37527</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12140,12 +12140,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12160,12 +12160,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>44830</t>
+          <t>43661</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>75638</t>
+          <t>74369</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12195,12 +12195,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>68328</t>
+          <t>67142</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>105062</t>
+          <t>104221</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12210,12 +12210,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -12238,12 +12238,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>35287</t>
+          <t>34743</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>60597</t>
+          <t>60039</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12273,12 +12273,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>113268</t>
+          <t>114983</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>159920</t>
+          <t>158039</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12308,12 +12308,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>156403</t>
+          <t>157716</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>210595</t>
+          <t>207633</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12323,12 +12323,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,62%</t>
         </is>
       </c>
     </row>
@@ -12351,12 +12351,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>187254</t>
+          <t>187509</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>217262</t>
+          <t>216450</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>806770</t>
+          <t>803263</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>860627</t>
+          <t>858283</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12421,12 +12421,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1002090</t>
+          <t>1003425</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1064395</t>
+          <t>1066081</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12436,12 +12436,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,21%</t>
         </is>
       </c>
     </row>
@@ -12581,12 +12581,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>66843</t>
+          <t>66076</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>104503</t>
+          <t>105815</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12596,12 +12596,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12616,12 +12616,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>64865</t>
+          <t>65729</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>102193</t>
+          <t>103654</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12631,12 +12631,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12651,12 +12651,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>143888</t>
+          <t>143168</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>195825</t>
+          <t>196711</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12666,12 +12666,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -12694,12 +12694,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>193460</t>
+          <t>192204</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>252977</t>
+          <t>254270</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12729,12 +12729,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>176796</t>
+          <t>174457</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>231308</t>
+          <t>231978</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12764,12 +12764,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>386353</t>
+          <t>385141</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>471326</t>
+          <t>463628</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12779,12 +12779,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -12807,12 +12807,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>559580</t>
+          <t>562495</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>650400</t>
+          <t>649895</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12842,12 +12842,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>498817</t>
+          <t>496161</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>578100</t>
+          <t>580763</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12877,12 +12877,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1081951</t>
+          <t>1081804</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1204861</t>
+          <t>1210122</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,93%</t>
         </is>
       </c>
     </row>
@@ -12920,12 +12920,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2351770</t>
+          <t>2346644</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2454367</t>
+          <t>2455870</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12935,12 +12935,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12955,12 +12955,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2563395</t>
+          <t>2562858</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2663589</t>
+          <t>2666188</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12990,12 +12990,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4942460</t>
+          <t>4946672</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5085260</t>
+          <t>5087738</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13005,12 +13005,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,37%</t>
         </is>
       </c>
     </row>
@@ -13189,7 +13189,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los días de diario en 2023</t>
+          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los días de diario en 2023 (tasa de respuesta: 99,59%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13389,7 +13389,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>835</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1576</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8124</t>
+          <t>8392</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13434,12 +13434,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1597</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8277</t>
+          <t>8586</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13474,7 +13474,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -13497,12 +13497,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11912</t>
+          <t>11865</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33259</t>
+          <t>34490</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13512,12 +13512,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8895</t>
+          <t>8968</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21338</t>
+          <t>22631</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13547,12 +13547,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24434</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50014</t>
+          <t>49285</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13582,12 +13582,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -13610,12 +13610,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36556</t>
+          <t>36254</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>64606</t>
+          <t>65109</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13625,12 +13625,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13645,12 +13645,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31114</t>
+          <t>30475</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54130</t>
+          <t>53798</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13660,12 +13660,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13680,12 +13680,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>74350</t>
+          <t>74910</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>109041</t>
+          <t>111570</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13695,12 +13695,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>417983</t>
+          <t>417888</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>451407</t>
+          <t>450785</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13738,12 +13738,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13758,12 +13758,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>373153</t>
+          <t>372887</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>398790</t>
+          <t>399393</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -13773,12 +13773,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13793,12 +13793,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>799508</t>
+          <t>797496</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>842352</t>
+          <t>840025</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13808,12 +13808,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,34%</t>
         </is>
       </c>
     </row>
@@ -13953,12 +13953,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8653</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -13968,12 +13968,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>655</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7460</t>
+          <t>6913</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14008,7 +14008,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>2966</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11680</t>
+          <t>11671</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14066,12 +14066,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11257</t>
+          <t>11252</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31624</t>
+          <t>31011</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14086,7 +14086,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14101,12 +14101,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12646</t>
+          <t>12617</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27239</t>
+          <t>28001</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14116,12 +14116,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14136,12 +14136,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27797</t>
+          <t>27087</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51476</t>
+          <t>52256</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14151,12 +14151,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -14179,12 +14179,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33881</t>
+          <t>34400</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58585</t>
+          <t>60010</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14194,12 +14194,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14214,12 +14214,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26407</t>
+          <t>25447</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45539</t>
+          <t>44956</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14229,12 +14229,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14249,12 +14249,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>64757</t>
+          <t>64257</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>96205</t>
+          <t>94811</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14264,12 +14264,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,38%</t>
         </is>
       </c>
     </row>
@@ -14292,12 +14292,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>365437</t>
+          <t>365948</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>397299</t>
+          <t>397975</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14307,12 +14307,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14327,12 +14327,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>312743</t>
+          <t>314269</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>336072</t>
+          <t>336588</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14342,12 +14342,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14362,12 +14362,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>688904</t>
+          <t>690745</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>727633</t>
+          <t>728675</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14377,12 +14377,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,44%</t>
         </is>
       </c>
     </row>
@@ -14522,12 +14522,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12939</t>
+          <t>13347</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14562,7 +14562,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2414</t>
+          <t>3498</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14577,7 +14577,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14592,12 +14592,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12835</t>
+          <t>13029</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14607,12 +14607,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -14635,12 +14635,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36899</t>
+          <t>36992</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -14650,12 +14650,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -14670,12 +14670,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1691</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8208</t>
+          <t>7661</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -14705,12 +14705,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>8156</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>39840</t>
+          <t>40718</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -14720,12 +14720,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -14748,12 +14748,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15646</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74329</t>
+          <t>73334</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14763,12 +14763,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14783,12 +14783,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7466</t>
+          <t>7515</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16602</t>
+          <t>16971</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14798,12 +14798,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14818,12 +14818,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20755</t>
+          <t>18443</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81844</t>
+          <t>84143</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -14861,12 +14861,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>549648</t>
+          <t>551519</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>640026</t>
+          <t>644358</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14876,12 +14876,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14896,12 +14896,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>143400</t>
+          <t>143578</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>154979</t>
+          <t>155033</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -14911,12 +14911,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -14931,12 +14931,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>704893</t>
+          <t>703840</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>801444</t>
+          <t>800133</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -14946,12 +14946,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,01%</t>
         </is>
       </c>
     </row>
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>6553</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21184</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15106,12 +15106,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15126,12 +15126,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13723</t>
+          <t>13585</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15141,12 +15141,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15161,12 +15161,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11001</t>
+          <t>11578</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28644</t>
+          <t>30568</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15176,12 +15176,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -15204,12 +15204,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>59168</t>
+          <t>58941</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>102502</t>
+          <t>102412</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15219,12 +15219,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15239,12 +15239,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22104</t>
+          <t>22303</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61783</t>
+          <t>62395</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15254,12 +15254,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15274,12 +15274,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>82781</t>
+          <t>81607</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>152236</t>
+          <t>152572</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15289,12 +15289,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -15317,12 +15317,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>117303</t>
+          <t>119847</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>169741</t>
+          <t>169335</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15332,12 +15332,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15352,12 +15352,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>65518</t>
+          <t>59735</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>148806</t>
+          <t>149243</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15367,12 +15367,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15387,12 +15387,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>169130</t>
+          <t>181230</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>295799</t>
+          <t>297081</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15402,12 +15402,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -15430,12 +15430,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>759237</t>
+          <t>756631</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>822498</t>
+          <t>818608</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15445,12 +15445,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15465,12 +15465,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>759858</t>
+          <t>759175</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>880096</t>
+          <t>887473</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15500,12 +15500,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1542774</t>
+          <t>1541188</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1727984</t>
+          <t>1721215</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15515,12 +15515,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,28%</t>
         </is>
       </c>
     </row>
@@ -15660,12 +15660,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2386</t>
+          <t>2562</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11847</t>
+          <t>10949</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15675,82 +15675,82 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>5878</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>2505</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>11657</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>6498</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>19542</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
           <t>0,5%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>5878</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>2465</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>12441</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
+      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>1,49%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>11657</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>6632</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>19699</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -15773,12 +15773,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20767</t>
+          <t>19962</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44092</t>
+          <t>42549</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -15788,12 +15788,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15808,12 +15808,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19222</t>
+          <t>19214</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39220</t>
+          <t>38399</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15828,7 +15828,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15843,12 +15843,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>44043</t>
+          <t>43148</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>74364</t>
+          <t>72857</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15858,12 +15858,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -15886,12 +15886,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>36200</t>
+          <t>35770</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>70746</t>
+          <t>69708</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -15901,12 +15901,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -15921,12 +15921,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>55338</t>
+          <t>55137</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>94177</t>
+          <t>93340</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -15936,12 +15936,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -15956,12 +15956,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>97022</t>
+          <t>97724</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>150285</t>
+          <t>149503</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -15971,12 +15971,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -15999,12 +15999,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>369440</t>
+          <t>368655</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>406261</t>
+          <t>406447</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -16014,12 +16014,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -16034,12 +16034,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>704170</t>
+          <t>706070</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>754974</t>
+          <t>755981</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -16049,12 +16049,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -16069,12 +16069,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1085500</t>
+          <t>1088755</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1154848</t>
+          <t>1153431</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -16084,12 +16084,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,95%</t>
         </is>
       </c>
     </row>
@@ -16229,12 +16229,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16244,12 +16244,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16264,12 +16264,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10331</t>
+          <t>9743</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16279,12 +16279,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16299,12 +16299,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2106</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>10093</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16314,12 +16314,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -16347,7 +16347,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11135</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16362,7 +16362,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16377,12 +16377,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>15041</t>
+          <t>15905</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>32580</t>
+          <t>34884</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16392,12 +16392,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16412,12 +16412,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>15997</t>
+          <t>16367</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>35691</t>
+          <t>36209</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16427,12 +16427,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -16455,12 +16455,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>23146</t>
+          <t>24533</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>71583</t>
+          <t>72034</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16470,12 +16470,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -16490,12 +16490,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>39459</t>
+          <t>38528</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>73612</t>
+          <t>71849</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -16505,12 +16505,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -16525,12 +16525,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>70875</t>
+          <t>70799</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>131975</t>
+          <t>133941</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16540,12 +16540,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -16568,12 +16568,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>165284</t>
+          <t>164916</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>213278</t>
+          <t>212400</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16583,12 +16583,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16603,12 +16603,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>656447</t>
+          <t>658703</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>694273</t>
+          <t>695861</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16618,12 +16618,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16638,12 +16638,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>835225</t>
+          <t>833678</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>899357</t>
+          <t>898490</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -16653,12 +16653,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,98%</t>
         </is>
       </c>
     </row>
@@ -16798,12 +16798,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>18957</t>
+          <t>18440</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>39153</t>
+          <t>39264</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16813,7 +16813,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -16833,12 +16833,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>16919</t>
+          <t>16512</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>35983</t>
+          <t>33675</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16848,12 +16848,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16868,12 +16868,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>41788</t>
+          <t>40318</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>68730</t>
+          <t>67340</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16883,12 +16883,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>130129</t>
+          <t>126596</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>206637</t>
+          <t>205657</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -16926,12 +16926,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -16946,12 +16946,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>107460</t>
+          <t>104673</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>157413</t>
+          <t>154151</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -16961,12 +16961,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -16981,12 +16981,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>254629</t>
+          <t>256597</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>344164</t>
+          <t>343886</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -16996,7 +16996,7 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -17024,12 +17024,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>283882</t>
+          <t>284160</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>424042</t>
+          <t>423564</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17039,12 +17039,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17059,12 +17059,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>271024</t>
+          <t>269497</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>366514</t>
+          <t>366434</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17074,12 +17074,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17094,12 +17094,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>585182</t>
+          <t>604300</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>765667</t>
+          <t>772898</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17109,12 +17109,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -17137,12 +17137,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2724411</t>
+          <t>2721910</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2915764</t>
+          <t>2925286</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17152,12 +17152,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17172,12 +17172,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3026404</t>
+          <t>3033159</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3163998</t>
+          <t>3167488</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17187,12 +17187,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17207,12 +17207,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>5786621</t>
+          <t>5772056</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6040777</t>
+          <t>6006434</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17222,12 +17222,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>86,77%</t>
         </is>
       </c>
     </row>
